--- a/MA2026-projeto-pratico/MA2026-entrega-parcial/01-excel/calendar.xlsx
+++ b/MA2026-projeto-pratico/MA2026-entrega-parcial/01-excel/calendar.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\fatecsp-MA20262-equipe-07-colossenses\MA2026-projeto-pratico\MA2026-entrega-parcial\01-excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5941006-332E-4D38-B662-EF1C44485461}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF1A7E76-BD2D-4412-8513-609FCB513ED9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="0" windowWidth="14985" windowHeight="9270" xr2:uid="{12D3D39E-1A24-42DA-8AD9-482000C10E20}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{12D3D39E-1A24-42DA-8AD9-482000C10E20}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -138,7 +138,32 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -149,6 +174,25 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A1030CB4-1960-493A-93C6-24EDA8128D7F}" name="calendar" displayName="calendar" ref="A1:J7" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A1:J7" xr:uid="{A1030CB4-1960-493A-93C6-24EDA8128D7F}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{8F48D102-2DF6-44DD-BBDF-63C975DF00BA}" name="service_id"/>
+    <tableColumn id="2" xr3:uid="{5EB407F1-ECA8-4B01-98EB-960C0FC50D66}" name="monday"/>
+    <tableColumn id="3" xr3:uid="{5931F279-4DD4-4BD8-81C1-0120D21199A4}" name="tuesday"/>
+    <tableColumn id="4" xr3:uid="{98A5786F-8981-4F97-9333-ABDE4F681888}" name="wednesday"/>
+    <tableColumn id="5" xr3:uid="{91B919AA-E316-4F1D-81B3-4E9C3F593E36}" name="thursday"/>
+    <tableColumn id="6" xr3:uid="{509F5215-2FF8-470C-B5AF-3D9BDA7FA61B}" name="friday"/>
+    <tableColumn id="7" xr3:uid="{A907DF15-6843-44E7-8346-87437F0A9FBC}" name="saturday "/>
+    <tableColumn id="8" xr3:uid="{F9779557-4EAE-4017-A83C-C71C19FE4259}" name="sunday"/>
+    <tableColumn id="9" xr3:uid="{88ED9829-CAB2-4829-AB13-3A14B81D78B4}" name="start_date" dataDxfId="2"/>
+    <tableColumn id="10" xr3:uid="{FB3BD23F-EB6D-4827-B249-AEA912189987}" name="end_date" dataDxfId="1"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -471,13 +515,14 @@
   <dimension ref="A1:J7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" customWidth="1"/>
-    <col min="2" max="2" width="10.140625" customWidth="1"/>
-    <col min="3" max="3" width="10" customWidth="1"/>
-    <col min="4" max="4" width="11.7109375" customWidth="1"/>
+    <col min="1" max="1" width="12.28515625" customWidth="1"/>
+    <col min="2" max="3" width="10.28515625" customWidth="1"/>
+    <col min="4" max="4" width="13.28515625" customWidth="1"/>
     <col min="5" max="5" width="13.42578125" customWidth="1"/>
-    <col min="9" max="9" width="10.7109375" customWidth="1"/>
-    <col min="10" max="10" width="10.5703125" customWidth="1"/>
+    <col min="7" max="7" width="11.28515625" customWidth="1"/>
+    <col min="8" max="8" width="9.5703125" customWidth="1"/>
+    <col min="9" max="9" width="12.140625" customWidth="1"/>
+    <col min="10" max="10" width="11.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -706,5 +751,8 @@
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>